--- a/docs/bazaar.xlsx
+++ b/docs/bazaar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Files\game-aux\bazaar\bazaar-arena\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0DFD8F6-3AA6-45D7-8B1F-70F7438776A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9857E387-9461-43D7-82CC-41B6D34EDF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{5A85A82F-ADC3-4846-8372-52BFBF2630DF}"/>
+    <workbookView xWindow="-98" yWindow="13403" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{5A85A82F-ADC3-4846-8372-52BFBF2630DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Vanessa" sheetId="1" r:id="rId1"/>
@@ -13537,15 +13537,15 @@
         <v>629</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" ht="46.5" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>569</v>
+        <v>628</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>649</v>
+        <v>630</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>393</v>
@@ -13560,13 +13560,13 @@
         <v>4</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>396</v>
+        <v>78</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>573</v>
+        <v>719</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
@@ -13574,10 +13574,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>570</v>
+        <v>645</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>393</v>
@@ -13592,24 +13592,22 @@
         <v>4</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>396</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="I4" s="6"/>
       <c r="J4" s="3" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="63" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>571</v>
+        <v>606</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>652</v>
+        <v>609</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>393</v>
@@ -13624,22 +13622,24 @@
         <v>4</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="I5" s="1"/>
+        <v>318</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>607</v>
+      </c>
       <c r="J5" s="3" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="48" x14ac:dyDescent="0.4">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="61.5" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>576</v>
+        <v>615</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>653</v>
+        <v>616</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>393</v>
@@ -13654,24 +13654,24 @@
         <v>4</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>577</v>
+        <v>304</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>578</v>
+        <v>607</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>393</v>
@@ -13686,24 +13686,24 @@
         <v>4</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>78</v>
+        <v>311</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>592</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="81" x14ac:dyDescent="0.4">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>393</v>
@@ -13717,14 +13717,14 @@
       <c r="G8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>318</v>
+      <c r="H8" s="7" t="s">
+        <v>325</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>396</v>
+        <v>589</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>703</v>
+        <v>590</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="46.5" x14ac:dyDescent="0.4">
@@ -13732,10 +13732,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>583</v>
+        <v>639</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>656</v>
+        <v>641</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>393</v>
@@ -13750,24 +13750,24 @@
         <v>4</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>325</v>
+        <v>640</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>34</v>
+        <v>607</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="48" x14ac:dyDescent="0.4">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>394</v>
+        <v>624</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>657</v>
+        <v>626</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>393</v>
@@ -13782,13 +13782,13 @@
         <v>4</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>325</v>
+        <v>572</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>34</v>
+        <v>256</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
@@ -13796,10 +13796,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>395</v>
+        <v>599</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>658</v>
+        <v>600</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>393</v>
@@ -13814,24 +13814,24 @@
         <v>4</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="I11" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>396</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="46.5" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>584</v>
+        <v>625</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>659</v>
+        <v>627</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>393</v>
@@ -13846,22 +13846,24 @@
         <v>4</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="I12" s="6"/>
+        <v>317</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="J12" s="3" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="49.5" x14ac:dyDescent="0.4">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="48" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>393</v>
@@ -13876,22 +13878,24 @@
         <v>4</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="I13" s="6"/>
+        <v>577</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>578</v>
+      </c>
       <c r="J13" s="3" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>588</v>
+        <v>610</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>647</v>
+        <v>612</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>393</v>
@@ -13905,25 +13909,23 @@
       <c r="G14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>589</v>
-      </c>
+      <c r="I14" s="6"/>
       <c r="J14" s="3" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>393</v>
@@ -13938,24 +13940,24 @@
         <v>4</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>592</v>
+        <v>318</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>589</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="33" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>587</v>
+        <v>601</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>750</v>
+        <v>602</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>393</v>
@@ -13972,22 +13974,20 @@
       <c r="H16" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>589</v>
-      </c>
+      <c r="I16" s="6"/>
       <c r="J16" s="3" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="33" x14ac:dyDescent="0.4">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>594</v>
+        <v>617</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>595</v>
+        <v>619</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>393</v>
@@ -14002,24 +14002,24 @@
         <v>4</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>56</v>
+        <v>311</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>589</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="48" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>597</v>
+        <v>394</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>598</v>
+        <v>657</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>393</v>
@@ -14034,13 +14034,13 @@
         <v>4</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>589</v>
+        <v>325</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
@@ -14048,10 +14048,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>599</v>
+        <v>633</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>600</v>
+        <v>634</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>393</v>
@@ -14069,21 +14069,21 @@
         <v>325</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>396</v>
+        <v>589</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="33" x14ac:dyDescent="0.4">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>601</v>
+        <v>635</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>602</v>
+        <v>636</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>393</v>
@@ -14098,22 +14098,24 @@
         <v>4</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="I20" s="6"/>
+        <v>325</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>589</v>
+      </c>
       <c r="J20" s="3" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.4">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>393</v>
@@ -14128,24 +14130,24 @@
         <v>4</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>56</v>
+        <v>318</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>589</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="63" x14ac:dyDescent="0.4">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>606</v>
+        <v>570</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>609</v>
+        <v>651</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>393</v>
@@ -14160,24 +14162,24 @@
         <v>4</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>607</v>
+        <v>396</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="16.5" x14ac:dyDescent="0.4">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>393</v>
@@ -14194,20 +14196,22 @@
       <c r="H23" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="I23" s="6"/>
+      <c r="I23" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="J23" s="3" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="61.5" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>613</v>
+        <v>631</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>614</v>
+        <v>632</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>393</v>
@@ -14222,24 +14226,24 @@
         <v>4</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>589</v>
+        <v>325</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="61.5" x14ac:dyDescent="0.4">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="48" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>393</v>
@@ -14254,24 +14258,24 @@
         <v>4</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>607</v>
+        <v>157</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.4">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="81" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>617</v>
+        <v>582</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>619</v>
+        <v>655</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>393</v>
@@ -14286,24 +14290,24 @@
         <v>4</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>589</v>
+        <v>318</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>396</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="48" x14ac:dyDescent="0.4">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>620</v>
+        <v>569</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>621</v>
+        <v>649</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>393</v>
@@ -14318,13 +14322,13 @@
         <v>4</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>18</v>
+        <v>325</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>396</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>715</v>
+        <v>573</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
@@ -14359,15 +14363,15 @@
         <v>716</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:10" ht="46.5" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>624</v>
+        <v>583</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>393</v>
@@ -14382,13 +14386,13 @@
         <v>4</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>572</v>
+        <v>325</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>256</v>
+        <v>34</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="46.5" x14ac:dyDescent="0.4">
@@ -14396,10 +14400,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>393</v>
@@ -14414,24 +14418,24 @@
         <v>4</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>56</v>
+        <v>643</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="46.5" x14ac:dyDescent="0.4">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>628</v>
+        <v>395</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>630</v>
+        <v>658</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>393</v>
@@ -14448,22 +14452,22 @@
       <c r="H31" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="I31" s="6" t="s">
-        <v>78</v>
+      <c r="I31" s="1" t="s">
+        <v>396</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="61.5" x14ac:dyDescent="0.4">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>631</v>
+        <v>571</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>393</v>
@@ -14478,13 +14482,11 @@
         <v>4</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>256</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="I32" s="1"/>
       <c r="J32" s="3" t="s">
-        <v>720</v>
+        <v>575</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
@@ -14492,10 +14494,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>633</v>
+        <v>613</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>634</v>
+        <v>614</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>393</v>
@@ -14510,13 +14512,13 @@
         <v>4</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="I33" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="I33" s="8" t="s">
         <v>589</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
@@ -14524,10 +14526,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>635</v>
+        <v>580</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>636</v>
+        <v>654</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>393</v>
@@ -14542,13 +14544,13 @@
         <v>4</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>589</v>
+        <v>318</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>722</v>
+        <v>581</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="33" x14ac:dyDescent="0.4">
@@ -14583,15 +14585,15 @@
         <v>723</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="46.5" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A36" s="1">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>639</v>
+        <v>584</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>641</v>
+        <v>659</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>393</v>
@@ -14606,24 +14608,22 @@
         <v>4</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>640</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>607</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="I36" s="6"/>
       <c r="J36" s="3" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="46.5" x14ac:dyDescent="0.4">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="33" x14ac:dyDescent="0.4">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>642</v>
+        <v>594</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>393</v>
@@ -14638,24 +14638,24 @@
         <v>4</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>325</v>
+        <v>596</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>643</v>
+        <v>56</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="49.5" x14ac:dyDescent="0.4">
       <c r="A38" s="1">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>645</v>
+        <v>586</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>393</v>
@@ -14670,22 +14670,22 @@
         <v>4</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="I38" s="6"/>
       <c r="J38" s="3" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="46.5" x14ac:dyDescent="0.4">
       <c r="A39" s="1">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>661</v>
+        <v>687</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>666</v>
+        <v>689</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>393</v>
@@ -14700,24 +14700,24 @@
         <v>63</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>662</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>396</v>
+        <v>572</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="66" x14ac:dyDescent="0.4">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="112.5" x14ac:dyDescent="0.4">
       <c r="A40" s="1">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>664</v>
+        <v>697</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>667</v>
+        <v>698</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>393</v>
@@ -14732,24 +14732,24 @@
         <v>63</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>11</v>
+        <v>318</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="63" x14ac:dyDescent="0.4">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="61.5" x14ac:dyDescent="0.4">
       <c r="A41" s="1">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>668</v>
+        <v>690</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>669</v>
+        <v>691</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>393</v>
@@ -14764,24 +14764,24 @@
         <v>63</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>256</v>
+        <v>572</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="48" x14ac:dyDescent="0.4">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="31.9" x14ac:dyDescent="0.4">
       <c r="A42" s="1">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>670</v>
+        <v>702</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>673</v>
+        <v>739</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>393</v>
@@ -14796,24 +14796,21 @@
         <v>63</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>671</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>672</v>
+        <v>321</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="63" x14ac:dyDescent="0.4">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="48" x14ac:dyDescent="0.4">
       <c r="A43" s="1">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>393</v>
@@ -14828,22 +14825,24 @@
         <v>63</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="I43" s="6"/>
+        <v>671</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>672</v>
+      </c>
       <c r="J43" s="3" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="76.5" x14ac:dyDescent="0.4">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="46.5" x14ac:dyDescent="0.4">
       <c r="A44" s="1">
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>677</v>
+        <v>740</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>678</v>
+        <v>742</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>393</v>
@@ -14858,13 +14857,13 @@
         <v>63</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>11</v>
+        <v>317</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>730</v>
+        <v>741</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="76.5" x14ac:dyDescent="0.4">
@@ -14872,10 +14871,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>393</v>
@@ -14890,24 +14889,24 @@
         <v>63</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="I45" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="I45" s="6" t="s">
         <v>256</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="61.5" x14ac:dyDescent="0.4">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="76.5" x14ac:dyDescent="0.4">
       <c r="A46" s="1">
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>681</v>
+        <v>699</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>682</v>
+        <v>700</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>393</v>
@@ -14922,13 +14921,13 @@
         <v>63</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>18</v>
+        <v>256</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="46.5" x14ac:dyDescent="0.4">
@@ -14968,10 +14967,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>393</v>
@@ -14986,13 +14985,13 @@
         <v>63</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="I48" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="I48" s="8" t="s">
         <v>256</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="46.5" x14ac:dyDescent="0.4">
@@ -15000,10 +14999,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>687</v>
+        <v>744</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>689</v>
+        <v>749</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>393</v>
@@ -15020,22 +15019,22 @@
       <c r="H49" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="I49" s="8" t="s">
-        <v>18</v>
+      <c r="I49" s="6" t="s">
+        <v>747</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="61.5" x14ac:dyDescent="0.4">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="46.5" x14ac:dyDescent="0.4">
       <c r="A50" s="1">
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>393</v>
@@ -15056,18 +15055,18 @@
         <v>18</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="76.5" x14ac:dyDescent="0.4">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="61.5" x14ac:dyDescent="0.4">
       <c r="A51" s="1">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>692</v>
+        <v>743</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>693</v>
+        <v>746</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>393</v>
@@ -15085,21 +15084,21 @@
         <v>318</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>256</v>
+        <v>589</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="46.5" x14ac:dyDescent="0.4">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="63" x14ac:dyDescent="0.4">
       <c r="A52" s="1">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>694</v>
+        <v>668</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>696</v>
+        <v>669</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>393</v>
@@ -15114,24 +15113,24 @@
         <v>63</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>18</v>
+        <v>157</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="112.5" x14ac:dyDescent="0.4">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="31.5" x14ac:dyDescent="0.4">
       <c r="A53" s="1">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>697</v>
+        <v>661</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>698</v>
+        <v>666</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>393</v>
@@ -15146,13 +15145,13 @@
         <v>63</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="I53" s="8" t="s">
-        <v>256</v>
+        <v>662</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>396</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>701</v>
+        <v>663</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="76.5" x14ac:dyDescent="0.4">
@@ -15160,10 +15159,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>699</v>
+        <v>677</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>700</v>
+        <v>678</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>393</v>
@@ -15178,24 +15177,24 @@
         <v>63</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>256</v>
+        <v>318</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="31.9" x14ac:dyDescent="0.4">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="61.5" x14ac:dyDescent="0.4">
       <c r="A55" s="1">
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>702</v>
+        <v>681</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>739</v>
+        <v>682</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>393</v>
@@ -15210,21 +15209,24 @@
         <v>63</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="46.5" x14ac:dyDescent="0.4">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="76.5" x14ac:dyDescent="0.4">
       <c r="A56" s="1">
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>740</v>
+        <v>679</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>742</v>
+        <v>680</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>393</v>
@@ -15239,24 +15241,24 @@
         <v>63</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>16</v>
+        <v>318</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="61.5" x14ac:dyDescent="0.4">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="63" x14ac:dyDescent="0.4">
       <c r="A57" s="1">
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>743</v>
+        <v>674</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>746</v>
+        <v>676</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>393</v>
@@ -15271,24 +15273,22 @@
         <v>63</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="I57" s="8" t="s">
-        <v>589</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="I57" s="6"/>
       <c r="J57" s="3" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="46.5" x14ac:dyDescent="0.4">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="66" x14ac:dyDescent="0.4">
       <c r="A58" s="1">
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>744</v>
+        <v>664</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>749</v>
+        <v>667</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>393</v>
@@ -15303,13 +15303,13 @@
         <v>63</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>572</v>
+        <v>665</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>747</v>
+        <v>11</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>748</v>
+        <v>727</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.4">
